--- a/artfynd/A 37012-2022 artfynd.xlsx
+++ b/artfynd/A 37012-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 37012-2022 artfynd.xlsx
+++ b/artfynd/A 37012-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1577,6 +1577,130 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>131524647</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99023</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Linneberg, Nrk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>488084</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6565465</v>
+      </c>
+      <c r="S9" t="n">
+        <v>31</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Lekeberg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Knista</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>T-Lek-0027</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-03-29</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-03-29</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>ca</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Sofia Lund</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum, Amanda Olsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37012-2022 artfynd.xlsx
+++ b/artfynd/A 37012-2022 artfynd.xlsx
@@ -1582,7 +1582,7 @@
         <v>131524647</v>
       </c>
       <c r="B9" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 37012-2022 artfynd.xlsx
+++ b/artfynd/A 37012-2022 artfynd.xlsx
@@ -1582,7 +1582,7 @@
         <v>131524647</v>
       </c>
       <c r="B9" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 37012-2022 artfynd.xlsx
+++ b/artfynd/A 37012-2022 artfynd.xlsx
@@ -1582,7 +1582,7 @@
         <v>131524647</v>
       </c>
       <c r="B9" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 37012-2022 artfynd.xlsx
+++ b/artfynd/A 37012-2022 artfynd.xlsx
@@ -1582,7 +1582,7 @@
         <v>131524647</v>
       </c>
       <c r="B9" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 37012-2022 artfynd.xlsx
+++ b/artfynd/A 37012-2022 artfynd.xlsx
@@ -1582,7 +1582,7 @@
         <v>131524647</v>
       </c>
       <c r="B9" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 37012-2022 artfynd.xlsx
+++ b/artfynd/A 37012-2022 artfynd.xlsx
@@ -1582,7 +1582,7 @@
         <v>131524647</v>
       </c>
       <c r="B9" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 37012-2022 artfynd.xlsx
+++ b/artfynd/A 37012-2022 artfynd.xlsx
@@ -1582,7 +1582,7 @@
         <v>131524647</v>
       </c>
       <c r="B9" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 37012-2022 artfynd.xlsx
+++ b/artfynd/A 37012-2022 artfynd.xlsx
@@ -1582,7 +1582,7 @@
         <v>131524647</v>
       </c>
       <c r="B9" t="n">
-        <v>99044</v>
+        <v>99047</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 37012-2022 artfynd.xlsx
+++ b/artfynd/A 37012-2022 artfynd.xlsx
@@ -1582,7 +1582,7 @@
         <v>131524647</v>
       </c>
       <c r="B9" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 37012-2022 artfynd.xlsx
+++ b/artfynd/A 37012-2022 artfynd.xlsx
@@ -1582,7 +1582,7 @@
         <v>131524647</v>
       </c>
       <c r="B9" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 37012-2022 artfynd.xlsx
+++ b/artfynd/A 37012-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,51 +675,46 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99533028</v>
+        <v>99532935</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488075.219395762</v>
+        <v>488099</v>
       </c>
       <c r="R2" t="n">
-        <v>6565451.162957666</v>
+        <v>6565444</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,33 +755,17 @@
           <t>2022-03-29</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-03-29</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>ca</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -805,15 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>99532952</v>
+        <v>99532879</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -840,7 +814,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -857,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488084.438134556</v>
+        <v>488102</v>
       </c>
       <c r="R3" t="n">
-        <v>6565448.063351708</v>
+        <v>6565382</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,19 +864,9 @@
           <t>2022-03-29</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-03-29</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -935,15 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>99533041</v>
+        <v>99532908</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -970,7 +929,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -987,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488077.829320918</v>
+        <v>488096</v>
       </c>
       <c r="R4" t="n">
-        <v>6565465.996616755</v>
+        <v>6565388</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,19 +979,9 @@
           <t>2022-03-29</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-03-29</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1065,15 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>99532999</v>
+        <v>99532952</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1100,7 +1044,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1117,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488076.2672164982</v>
+        <v>488084</v>
       </c>
       <c r="R5" t="n">
-        <v>6565458.324706105</v>
+        <v>6565448</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1150,19 +1094,9 @@
           <t>2022-03-29</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-03-29</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1195,15 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>99532908</v>
+        <v>99532999</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1230,7 +1159,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1247,10 +1176,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488096.0426389378</v>
+        <v>488076</v>
       </c>
       <c r="R6" t="n">
-        <v>6565388.147273093</v>
+        <v>6565458</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1280,19 +1209,9 @@
           <t>2022-03-29</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-03-29</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1325,51 +1244,46 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>99532935</v>
+        <v>99533028</v>
       </c>
       <c r="B7" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1377,10 +1291,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488099.2948460479</v>
+        <v>488075</v>
       </c>
       <c r="R7" t="n">
-        <v>6565444.434342342</v>
+        <v>6565451</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1410,19 +1324,14 @@
           <t>2022-03-29</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-03-29</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>ca</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1431,6 +1340,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1449,15 +1359,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>99532879</v>
+        <v>99533041</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1501,10 +1406,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488102.1773765901</v>
+        <v>488078</v>
       </c>
       <c r="R8" t="n">
-        <v>6565382.498320307</v>
+        <v>6565466</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1534,19 +1439,9 @@
           <t>2022-03-29</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-03-29</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1579,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131524647</v>
+        <v>99533049</v>
       </c>
       <c r="B9" t="n">
-        <v>99054</v>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1609,12 +1504,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1626,13 +1521,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488084</v>
+        <v>488088</v>
       </c>
       <c r="R9" t="n">
-        <v>6565465</v>
+        <v>6565475</v>
       </c>
       <c r="S9" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1652,11 +1547,6 @@
       <c r="W9" t="inlineStr">
         <is>
           <t>Knista</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>T-Lek-0027</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1687,15 +1577,250 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum, Amanda Olsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>99533089</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Linneberg, Nrk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>488073</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6565485</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Lekeberg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Knista</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-03-29</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-03-29</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>ca</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum, Amanda Olsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>131524647</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Linneberg, Nrk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>488084</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6565465</v>
+      </c>
+      <c r="S11" t="n">
+        <v>31</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Lekeberg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Knista</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>T-Lek-0027</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2022-03-29</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2022-03-29</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>ca</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
           <t>Sofia Lund</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>Per Karlsson Linderum, Amanda Olsson</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr">
+      <c r="AY11" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
         </is>
